--- a/英语群_20260826.xlsx
+++ b/英语群_20260826.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huil\checkin\WeChatTextExport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huil\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1254,7 +1254,7 @@
       <c r="A1" s="24"/>
       <c r="B1" s="24">
         <f>SUM(B3:B1001)</f>
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C1" s="24">
         <f>SUM(C3:C1001)</f>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E1" s="24">
         <f>SUM(E3:E1001)</f>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="1"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="5">
         <v>0</v>
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="25">
         <v>25</v>
